--- a/data/raw/inventory/Week 35/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 35/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -1530,10 +1530,10 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -3018,10 +3018,10 @@
         <v>15</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         <v>11</v>
       </c>
       <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
         <v>1</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3204,10 +3204,10 @@
         <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -3446,25 +3446,25 @@
         </is>
       </c>
       <c r="E49" t="n">
+        <v>121</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
         <v>120</v>
       </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>18</v>
-      </c>
-      <c r="H49" t="n">
-        <v>102</v>
-      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -3957,10 +3957,10 @@
         <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -8052,10 +8052,10 @@
         <v>1</v>
       </c>
       <c r="K123" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
@@ -10520,10 +10520,10 @@
         <v>4</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
@@ -10582,10 +10582,10 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
@@ -11140,10 +11140,10 @@
         <v>2</v>
       </c>
       <c r="G173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
@@ -12008,10 +12008,10 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
@@ -12566,10 +12566,10 @@
         <v>21</v>
       </c>
       <c r="G196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I196" t="n">
         <v>0</v>
@@ -14116,10 +14116,10 @@
         <v>1</v>
       </c>
       <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
         <v>1</v>
-      </c>
-      <c r="H221" t="n">
-        <v>0</v>
       </c>
       <c r="I221" t="n">
         <v>0</v>
@@ -14175,7 +14175,7 @@
         <v>3</v>
       </c>
       <c r="F222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -14187,7 +14187,7 @@
         <v>0</v>
       </c>
       <c r="J222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K222" t="n">
         <v>3</v>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F225" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -14376,7 +14376,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L225" t="n">
         <v>0</v>
@@ -14860,10 +14860,10 @@
         <v>1</v>
       </c>
       <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
         <v>1</v>
-      </c>
-      <c r="H233" t="n">
-        <v>0</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
@@ -15666,10 +15666,10 @@
         <v>0</v>
       </c>
       <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
         <v>1</v>
-      </c>
-      <c r="H246" t="n">
-        <v>0</v>
       </c>
       <c r="I246" t="n">
         <v>0</v>
@@ -18636,25 +18636,25 @@
         </is>
       </c>
       <c r="E294" t="n">
+        <v>2</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" t="n">
+        <v>0</v>
+      </c>
+      <c r="H294" t="n">
+        <v>0</v>
+      </c>
+      <c r="I294" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" t="n">
         <v>1</v>
       </c>
-      <c r="F294" t="n">
-        <v>0</v>
-      </c>
-      <c r="G294" t="n">
-        <v>0</v>
-      </c>
-      <c r="H294" t="n">
-        <v>0</v>
-      </c>
-      <c r="I294" t="n">
-        <v>0</v>
-      </c>
-      <c r="J294" t="n">
-        <v>0</v>
-      </c>
       <c r="K294" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L294" t="n">
         <v>2</v>
@@ -18760,10 +18760,10 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F296" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G296" t="n">
         <v>0</v>
@@ -18778,7 +18778,7 @@
         <v>0</v>
       </c>
       <c r="K296" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L296" t="n">
         <v>2</v>
@@ -19014,10 +19014,10 @@
         <v>93</v>
       </c>
       <c r="G300" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H300" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I300" t="n">
         <v>0</v>
@@ -19194,7 +19194,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F303" t="n">
         <v>199</v>
@@ -19209,10 +19209,10 @@
         <v>0</v>
       </c>
       <c r="J303" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K303" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L303" t="n">
         <v>2</v>
@@ -19820,10 +19820,10 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I313" t="n">
         <v>0</v>
@@ -22852,10 +22852,10 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="F362" t="n">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="G362" t="n">
         <v>0</v>
@@ -22867,10 +22867,10 @@
         <v>0</v>
       </c>
       <c r="J362" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K362" t="n">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="L362" t="n">
         <v>4</v>
@@ -22917,7 +22917,7 @@
         <v>604</v>
       </c>
       <c r="F363" t="n">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G363" t="n">
         <v>0</v>
@@ -22929,7 +22929,7 @@
         <v>0</v>
       </c>
       <c r="J363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K363" t="n">
         <v>604</v>
@@ -23664,10 +23664,10 @@
         <v>21</v>
       </c>
       <c r="G375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H375" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I375" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F382" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G382" t="n">
         <v>0</v>
@@ -24110,7 +24110,7 @@
         <v>0</v>
       </c>
       <c r="K382" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L382" t="n">
         <v>0</v>
@@ -25580,17 +25580,17 @@
         </is>
       </c>
       <c r="E406" t="n">
+        <v>5</v>
+      </c>
+      <c r="F406" t="n">
         <v>4</v>
       </c>
-      <c r="F406" t="n">
-        <v>3</v>
-      </c>
       <c r="G406" t="n">
+        <v>0</v>
+      </c>
+      <c r="H406" t="n">
         <v>1</v>
       </c>
-      <c r="H406" t="n">
-        <v>0</v>
-      </c>
       <c r="I406" t="n">
         <v>0</v>
       </c>
@@ -25598,7 +25598,7 @@
         <v>0</v>
       </c>
       <c r="K406" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L406" t="n">
         <v>0</v>
@@ -26386,10 +26386,10 @@
         </is>
       </c>
       <c r="E419" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F419" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G419" t="n">
         <v>0</v>
@@ -26404,7 +26404,7 @@
         <v>0</v>
       </c>
       <c r="K419" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L419" t="n">
         <v>0</v>
@@ -26516,10 +26516,10 @@
         <v>0</v>
       </c>
       <c r="G421" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H421" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I421" t="n">
         <v>0</v>
@@ -28314,10 +28314,10 @@
         <v>0</v>
       </c>
       <c r="G450" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H450" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I450" t="n">
         <v>0</v>
@@ -28804,10 +28804,10 @@
         </is>
       </c>
       <c r="E458" t="n">
+        <v>6</v>
+      </c>
+      <c r="F458" t="n">
         <v>5</v>
-      </c>
-      <c r="F458" t="n">
-        <v>4</v>
       </c>
       <c r="G458" t="n">
         <v>0</v>
@@ -28822,7 +28822,7 @@
         <v>0</v>
       </c>
       <c r="K458" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L458" t="n">
         <v>0</v>
@@ -28931,7 +28931,7 @@
         <v>7</v>
       </c>
       <c r="F460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G460" t="n">
         <v>0</v>
@@ -28943,7 +28943,7 @@
         <v>0</v>
       </c>
       <c r="J460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K460" t="n">
         <v>7</v>
@@ -29678,10 +29678,10 @@
         <v>6</v>
       </c>
       <c r="G472" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H472" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I472" t="n">
         <v>0</v>
@@ -30230,16 +30230,16 @@
         </is>
       </c>
       <c r="E481" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F481" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G481" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H481" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I481" t="n">
         <v>0</v>
@@ -30248,7 +30248,7 @@
         <v>1</v>
       </c>
       <c r="K481" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L481" t="n">
         <v>0</v>
